--- a/tests/TC-11/results/timetable_all_departments_even.xlsx
+++ b/tests/TC-11/results/timetable_all_departments_even.xlsx
@@ -57,7 +57,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -78,6 +78,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00E1BEE7"/>
+        <bgColor rgb="00E1BEE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E0E0E0"/>
         <bgColor rgb="00E0E0E0"/>
       </patternFill>
@@ -90,8 +96,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFD0E6"/>
+        <bgColor rgb="00FFD0E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CDEFEA"/>
+        <bgColor rgb="00CDEFEA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00C8E6C9"/>
         <bgColor rgb="00C8E6C9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3BF"/>
+        <bgColor rgb="00FFF3BF"/>
       </patternFill>
     </fill>
     <fill>
@@ -159,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -167,13 +191,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -183,34 +207,58 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
@@ -669,7 +717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U16"/>
+  <dimension ref="A1:U21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -815,30 +863,44 @@
       </c>
       <c r="C2" s="8" t="inlineStr"/>
       <c r="D2" s="8" t="inlineStr"/>
-      <c r="E2" s="8" t="inlineStr"/>
-      <c r="F2" s="8" t="inlineStr"/>
-      <c r="G2" s="8" t="inlineStr"/>
-      <c r="H2" s="8" t="inlineStr"/>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>CS163
+LEC
+Room: 102
+Dr. Vivekraj</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="10" t="n"/>
+      <c r="H2" s="11" t="n"/>
       <c r="I2" s="8" t="inlineStr"/>
       <c r="J2" s="8" t="inlineStr"/>
       <c r="K2" s="8" t="inlineStr"/>
-      <c r="L2" s="9" t="inlineStr">
+      <c r="L2" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
       <c r="M2" s="8" t="inlineStr"/>
-      <c r="N2" s="8" t="inlineStr"/>
-      <c r="O2" s="8" t="inlineStr"/>
-      <c r="P2" s="8" t="inlineStr"/>
-      <c r="Q2" s="10" t="inlineStr">
+      <c r="N2" s="13" t="inlineStr">
         <is>
           <t>B1
 LEC</t>
         </is>
       </c>
-      <c r="R2" s="11" t="n"/>
-      <c r="S2" s="12" t="n"/>
+      <c r="O2" s="10" t="n"/>
+      <c r="P2" s="11" t="n"/>
+      <c r="Q2" s="8" t="inlineStr"/>
+      <c r="R2" s="14" t="inlineStr">
+        <is>
+          <t>MA163
+TUT
+Room: 102
+Dr. Anand</t>
+        </is>
+      </c>
+      <c r="S2" s="11" t="n"/>
       <c r="T2" s="8" t="inlineStr"/>
       <c r="U2" s="7" t="inlineStr">
         <is>
@@ -858,29 +920,106 @@
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr"/>
-      <c r="D3" s="8" t="inlineStr"/>
-      <c r="E3" s="8" t="inlineStr"/>
-      <c r="F3" s="8" t="inlineStr"/>
-      <c r="G3" s="8" t="inlineStr"/>
-      <c r="H3" s="8" t="inlineStr"/>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>CS163
+LAB
+Room: L101+L102
+Dr. Vivekraj</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
       <c r="I3" s="8" t="inlineStr"/>
       <c r="J3" s="8" t="inlineStr"/>
       <c r="K3" s="8" t="inlineStr"/>
-      <c r="L3" s="9" t="inlineStr">
+      <c r="L3" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
       <c r="M3" s="8" t="inlineStr"/>
-      <c r="N3" s="10" t="inlineStr">
+      <c r="N3" s="9" t="inlineStr">
+        <is>
+          <t>CS163
+LEC
+Room: 102
+Dr. Vivekraj</t>
+        </is>
+      </c>
+      <c r="O3" s="10" t="n"/>
+      <c r="P3" s="11" t="n"/>
+      <c r="Q3" s="8" t="inlineStr"/>
+      <c r="R3" s="8" t="inlineStr"/>
+      <c r="S3" s="8" t="inlineStr"/>
+      <c r="T3" s="15" t="inlineStr">
+        <is>
+          <t>B4
+TUT</t>
+        </is>
+      </c>
+      <c r="U3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>CS208
+LEC
+Room: 101
+Dr. Prabhu</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="8" t="inlineStr"/>
+      <c r="F4" s="17" t="inlineStr">
+        <is>
+          <t>B2
+LEC</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>B1
 TUT</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr"/>
-      <c r="P3" s="8" t="inlineStr"/>
-      <c r="Q3" s="13" t="inlineStr">
+      <c r="H4" s="10" t="n"/>
+      <c r="I4" s="11" t="n"/>
+      <c r="J4" s="8" t="inlineStr"/>
+      <c r="K4" s="8" t="inlineStr"/>
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M4" s="18" t="inlineStr">
+        <is>
+          <t>CS162
+LEC
+Room: 102
+Dr. Guha</t>
+        </is>
+      </c>
+      <c r="N4" s="11" t="n"/>
+      <c r="O4" s="8" t="inlineStr"/>
+      <c r="P4" s="8" t="inlineStr"/>
+      <c r="Q4" s="14" t="inlineStr">
         <is>
           <t>MA163
 LEC
@@ -888,31 +1027,126 @@
 Dr. Anand</t>
         </is>
       </c>
-      <c r="R3" s="11" t="n"/>
-      <c r="S3" s="12" t="n"/>
-      <c r="T3" s="8" t="inlineStr"/>
-      <c r="U3" s="7" t="inlineStr">
+      <c r="R4" s="10" t="n"/>
+      <c r="S4" s="11" t="n"/>
+      <c r="T4" s="8" t="inlineStr"/>
+      <c r="U4" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="40" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr"/>
-      <c r="D4" s="8" t="inlineStr"/>
-      <c r="E4" s="8" t="inlineStr"/>
-      <c r="F4" s="8" t="inlineStr"/>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>B2
+LEC</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
+      <c r="G5" s="11" t="n"/>
+      <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr"/>
+      <c r="J5" s="8" t="inlineStr"/>
+      <c r="K5" s="8" t="inlineStr"/>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M5" s="18" t="inlineStr">
+        <is>
+          <t>CS162
+LEC
+Room: 102
+Dr. Guha</t>
+        </is>
+      </c>
+      <c r="N5" s="11" t="n"/>
+      <c r="O5" s="8" t="inlineStr"/>
+      <c r="P5" s="8" t="inlineStr"/>
+      <c r="Q5" s="15" t="inlineStr">
+        <is>
+          <t>B4
+LEC</t>
+        </is>
+      </c>
+      <c r="R5" s="10" t="n"/>
+      <c r="S5" s="11" t="n"/>
+      <c r="T5" s="8" t="inlineStr"/>
+      <c r="U5" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>B2
+TUT</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr"/>
+      <c r="E6" s="8" t="inlineStr"/>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>B1
+LEC</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="n"/>
+      <c r="H6" s="10" t="n"/>
+      <c r="I6" s="11" t="n"/>
+      <c r="J6" s="8" t="inlineStr"/>
+      <c r="K6" s="8" t="inlineStr"/>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M6" s="15" t="inlineStr">
+        <is>
+          <t>B4
+LEC</t>
+        </is>
+      </c>
+      <c r="N6" s="11" t="n"/>
+      <c r="O6" s="8" t="inlineStr"/>
+      <c r="P6" s="14" t="inlineStr">
+        <is>
+          <t>MA163
+LEC
+Room: 101
+Dr. Anand</t>
+        </is>
+      </c>
+      <c r="Q6" s="10" t="n"/>
+      <c r="R6" s="11" t="n"/>
+      <c r="S6" s="8" t="inlineStr"/>
+      <c r="T6" s="18" t="inlineStr">
         <is>
           <t>CS162
 TUT
@@ -920,328 +1154,348 @@
 Dr. Guha</t>
         </is>
       </c>
-      <c r="H4" s="12" t="n"/>
-      <c r="I4" s="8" t="inlineStr"/>
-      <c r="J4" s="8" t="inlineStr"/>
-      <c r="K4" s="8" t="inlineStr"/>
-      <c r="L4" s="9" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M4" s="8" t="inlineStr"/>
-      <c r="N4" s="13" t="inlineStr">
-        <is>
-          <t>MA163
-TUT
-Room: 101
-Dr. Anand</t>
-        </is>
-      </c>
-      <c r="O4" s="8" t="inlineStr"/>
-      <c r="P4" s="8" t="inlineStr"/>
-      <c r="Q4" s="8" t="inlineStr"/>
-      <c r="R4" s="8" t="inlineStr"/>
-      <c r="S4" s="8" t="inlineStr"/>
-      <c r="T4" s="8" t="inlineStr"/>
-      <c r="U4" s="7" t="inlineStr">
+      <c r="U6" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr"/>
-      <c r="D5" s="8" t="inlineStr"/>
-      <c r="E5" s="8" t="inlineStr"/>
-      <c r="F5" s="8" t="inlineStr"/>
-      <c r="G5" s="14" t="inlineStr">
-        <is>
-          <t>CS162
-LEC
-Room: 101
-Dr. Guha</t>
-        </is>
-      </c>
-      <c r="H5" s="11" t="n"/>
-      <c r="I5" s="11" t="n"/>
-      <c r="J5" s="12" t="n"/>
-      <c r="K5" s="8" t="inlineStr"/>
-      <c r="L5" s="9" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M5" s="13" t="inlineStr">
-        <is>
-          <t>MA163
-LEC
-Room: 101
-Dr. Anand</t>
-        </is>
-      </c>
-      <c r="N5" s="12" t="n"/>
-      <c r="O5" s="8" t="inlineStr"/>
-      <c r="P5" s="8" t="inlineStr"/>
-      <c r="Q5" s="8" t="inlineStr"/>
-      <c r="R5" s="8" t="inlineStr"/>
-      <c r="S5" s="8" t="inlineStr"/>
-      <c r="T5" s="8" t="inlineStr"/>
-      <c r="U5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C6" s="14" t="inlineStr">
-        <is>
-          <t>CS162
-LEC
-Room: 101
-Dr. Guha</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="n"/>
-      <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="8" t="inlineStr"/>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>B1
-LEC</t>
-        </is>
-      </c>
-      <c r="H6" s="11" t="n"/>
-      <c r="I6" s="11" t="n"/>
-      <c r="J6" s="12" t="n"/>
-      <c r="K6" s="8" t="inlineStr"/>
-      <c r="L6" s="9" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M6" s="8" t="inlineStr"/>
-      <c r="N6" s="8" t="inlineStr"/>
-      <c r="O6" s="8" t="inlineStr"/>
-      <c r="P6" s="8" t="inlineStr"/>
-      <c r="Q6" s="8" t="inlineStr"/>
-      <c r="R6" s="8" t="inlineStr"/>
-      <c r="S6" s="8" t="inlineStr"/>
-      <c r="T6" s="8" t="inlineStr"/>
-      <c r="U6" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>Course Details</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>Course Code</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>Color</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>Name of the Course</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>Course Co-ordinator</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>LTPSC</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>Room Number</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>B1-CS154</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr"/>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>Intro Data Analytics</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr"/>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>Data Analytics</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>Dr. Abdul</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>3-1-0-0-2</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t>103</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>B1-EC156</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr"/>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>Intro Sensors</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr"/>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>Sensor Tech</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>Dr. Eswaran</t>
         </is>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>3-1-0-0-2</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>B1-ASD152</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr"/>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>Visual Design</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>Dr. Sandesh</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>3-1-0-0-2</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t>102</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>B1-ASD152</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr"/>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>Visual Design</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>Dr. Sandesh</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="21" t="inlineStr">
+        <is>
+          <t>B2-DS151</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr"/>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>Linux</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>Dr. Layek</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>3-1-0-0-2</t>
         </is>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="21" t="inlineStr">
+        <is>
+          <t>B2-CS151</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr"/>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>Cybersecurity</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>Dr. Rajendra</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>3-1-0-0-2</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="17" t="inlineStr">
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="21" t="inlineStr">
+        <is>
+          <t>B4-HS159</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr"/>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>Quantum Physics</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>Dr. Physics</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>3-1-0-0-2</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="21" t="inlineStr">
         <is>
           <t>MA163</t>
         </is>
       </c>
-      <c r="B15" s="19" t="inlineStr"/>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="B18" s="25" t="inlineStr"/>
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>Linear Algebra</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>Dr. Anand</t>
         </is>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="E18" s="21" t="inlineStr">
         <is>
           <t>3-1-0-0-2</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="17" t="inlineStr">
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="21" t="inlineStr">
         <is>
           <t>CS162</t>
         </is>
       </c>
-      <c r="B16" s="20" t="inlineStr"/>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="B19" s="26" t="inlineStr"/>
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>Optimization</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>Dr. Guha</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>3-1-0-0-2</t>
         </is>
       </c>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="21" t="inlineStr">
+        <is>
+          <t>CS163</t>
+        </is>
+      </c>
+      <c r="B20" s="27" t="inlineStr"/>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>Data Structures</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>Dr. Vivekraj</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>3-0-2-0-4</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="21" t="inlineStr">
+        <is>
+          <t>CS208</t>
+        </is>
+      </c>
+      <c r="B21" s="28" t="inlineStr"/>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>Computer Architecture</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>Dr. Prabhu</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>3-0-2-0-2</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="C6:D6"/>
+  <mergeCells count="15">
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="Q4:S4"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="P6:R6"/>
     <mergeCell ref="M5:N5"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="Q3:S3"/>
+    <mergeCell ref="D5:G5"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="C4:D4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1254,7 +1508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U16"/>
+  <dimension ref="A1:U21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1400,30 +1654,44 @@
       </c>
       <c r="C2" s="8" t="inlineStr"/>
       <c r="D2" s="8" t="inlineStr"/>
-      <c r="E2" s="8" t="inlineStr"/>
-      <c r="F2" s="8" t="inlineStr"/>
-      <c r="G2" s="8" t="inlineStr"/>
-      <c r="H2" s="8" t="inlineStr"/>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>CS163
+LEC
+Room: 102
+Dr. Vivekraj</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="10" t="n"/>
+      <c r="H2" s="11" t="n"/>
       <c r="I2" s="8" t="inlineStr"/>
       <c r="J2" s="8" t="inlineStr"/>
       <c r="K2" s="8" t="inlineStr"/>
-      <c r="L2" s="9" t="inlineStr">
+      <c r="L2" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
       <c r="M2" s="8" t="inlineStr"/>
-      <c r="N2" s="8" t="inlineStr"/>
-      <c r="O2" s="8" t="inlineStr"/>
-      <c r="P2" s="8" t="inlineStr"/>
-      <c r="Q2" s="10" t="inlineStr">
+      <c r="N2" s="13" t="inlineStr">
         <is>
           <t>B1
 LEC</t>
         </is>
       </c>
-      <c r="R2" s="11" t="n"/>
-      <c r="S2" s="12" t="n"/>
+      <c r="O2" s="10" t="n"/>
+      <c r="P2" s="11" t="n"/>
+      <c r="Q2" s="8" t="inlineStr"/>
+      <c r="R2" s="14" t="inlineStr">
+        <is>
+          <t>MA163
+TUT
+Room: 102
+Dr. Anand</t>
+        </is>
+      </c>
+      <c r="S2" s="11" t="n"/>
       <c r="T2" s="8" t="inlineStr"/>
       <c r="U2" s="7" t="inlineStr">
         <is>
@@ -1443,29 +1711,106 @@
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr"/>
-      <c r="D3" s="8" t="inlineStr"/>
-      <c r="E3" s="8" t="inlineStr"/>
-      <c r="F3" s="8" t="inlineStr"/>
-      <c r="G3" s="8" t="inlineStr"/>
-      <c r="H3" s="8" t="inlineStr"/>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>CS163
+LAB
+Room: L101+L102
+Dr. Vivekraj</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
       <c r="I3" s="8" t="inlineStr"/>
       <c r="J3" s="8" t="inlineStr"/>
       <c r="K3" s="8" t="inlineStr"/>
-      <c r="L3" s="9" t="inlineStr">
+      <c r="L3" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
       <c r="M3" s="8" t="inlineStr"/>
-      <c r="N3" s="10" t="inlineStr">
+      <c r="N3" s="9" t="inlineStr">
+        <is>
+          <t>CS163
+LEC
+Room: 102
+Dr. Vivekraj</t>
+        </is>
+      </c>
+      <c r="O3" s="10" t="n"/>
+      <c r="P3" s="11" t="n"/>
+      <c r="Q3" s="8" t="inlineStr"/>
+      <c r="R3" s="8" t="inlineStr"/>
+      <c r="S3" s="8" t="inlineStr"/>
+      <c r="T3" s="15" t="inlineStr">
+        <is>
+          <t>B4
+TUT</t>
+        </is>
+      </c>
+      <c r="U3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>CS208
+LEC
+Room: 101
+Dr. Prabhu</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="8" t="inlineStr"/>
+      <c r="F4" s="17" t="inlineStr">
+        <is>
+          <t>B2
+LEC</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>B1
 TUT</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr"/>
-      <c r="P3" s="8" t="inlineStr"/>
-      <c r="Q3" s="13" t="inlineStr">
+      <c r="H4" s="10" t="n"/>
+      <c r="I4" s="11" t="n"/>
+      <c r="J4" s="8" t="inlineStr"/>
+      <c r="K4" s="8" t="inlineStr"/>
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M4" s="18" t="inlineStr">
+        <is>
+          <t>CS162
+LEC
+Room: 102
+Dr. Guha</t>
+        </is>
+      </c>
+      <c r="N4" s="11" t="n"/>
+      <c r="O4" s="8" t="inlineStr"/>
+      <c r="P4" s="8" t="inlineStr"/>
+      <c r="Q4" s="14" t="inlineStr">
         <is>
           <t>MA163
 LEC
@@ -1473,31 +1818,126 @@
 Dr. Anand</t>
         </is>
       </c>
-      <c r="R3" s="11" t="n"/>
-      <c r="S3" s="12" t="n"/>
-      <c r="T3" s="8" t="inlineStr"/>
-      <c r="U3" s="7" t="inlineStr">
+      <c r="R4" s="10" t="n"/>
+      <c r="S4" s="11" t="n"/>
+      <c r="T4" s="8" t="inlineStr"/>
+      <c r="U4" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="40" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr"/>
-      <c r="D4" s="8" t="inlineStr"/>
-      <c r="E4" s="8" t="inlineStr"/>
-      <c r="F4" s="8" t="inlineStr"/>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>B2
+LEC</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
+      <c r="G5" s="11" t="n"/>
+      <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr"/>
+      <c r="J5" s="8" t="inlineStr"/>
+      <c r="K5" s="8" t="inlineStr"/>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M5" s="18" t="inlineStr">
+        <is>
+          <t>CS162
+LEC
+Room: 102
+Dr. Guha</t>
+        </is>
+      </c>
+      <c r="N5" s="11" t="n"/>
+      <c r="O5" s="8" t="inlineStr"/>
+      <c r="P5" s="8" t="inlineStr"/>
+      <c r="Q5" s="15" t="inlineStr">
+        <is>
+          <t>B4
+LEC</t>
+        </is>
+      </c>
+      <c r="R5" s="10" t="n"/>
+      <c r="S5" s="11" t="n"/>
+      <c r="T5" s="8" t="inlineStr"/>
+      <c r="U5" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>B2
+TUT</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr"/>
+      <c r="E6" s="8" t="inlineStr"/>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>B1
+LEC</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="n"/>
+      <c r="H6" s="10" t="n"/>
+      <c r="I6" s="11" t="n"/>
+      <c r="J6" s="8" t="inlineStr"/>
+      <c r="K6" s="8" t="inlineStr"/>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M6" s="15" t="inlineStr">
+        <is>
+          <t>B4
+LEC</t>
+        </is>
+      </c>
+      <c r="N6" s="11" t="n"/>
+      <c r="O6" s="8" t="inlineStr"/>
+      <c r="P6" s="14" t="inlineStr">
+        <is>
+          <t>MA163
+LEC
+Room: 101
+Dr. Anand</t>
+        </is>
+      </c>
+      <c r="Q6" s="10" t="n"/>
+      <c r="R6" s="11" t="n"/>
+      <c r="S6" s="8" t="inlineStr"/>
+      <c r="T6" s="18" t="inlineStr">
         <is>
           <t>CS162
 TUT
@@ -1505,328 +1945,348 @@
 Dr. Guha</t>
         </is>
       </c>
-      <c r="H4" s="12" t="n"/>
-      <c r="I4" s="8" t="inlineStr"/>
-      <c r="J4" s="8" t="inlineStr"/>
-      <c r="K4" s="8" t="inlineStr"/>
-      <c r="L4" s="9" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M4" s="8" t="inlineStr"/>
-      <c r="N4" s="13" t="inlineStr">
-        <is>
-          <t>MA163
-TUT
-Room: 101
-Dr. Anand</t>
-        </is>
-      </c>
-      <c r="O4" s="8" t="inlineStr"/>
-      <c r="P4" s="8" t="inlineStr"/>
-      <c r="Q4" s="8" t="inlineStr"/>
-      <c r="R4" s="8" t="inlineStr"/>
-      <c r="S4" s="8" t="inlineStr"/>
-      <c r="T4" s="8" t="inlineStr"/>
-      <c r="U4" s="7" t="inlineStr">
+      <c r="U6" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr"/>
-      <c r="D5" s="8" t="inlineStr"/>
-      <c r="E5" s="8" t="inlineStr"/>
-      <c r="F5" s="8" t="inlineStr"/>
-      <c r="G5" s="14" t="inlineStr">
-        <is>
-          <t>CS162
-LEC
-Room: 101
-Dr. Guha</t>
-        </is>
-      </c>
-      <c r="H5" s="11" t="n"/>
-      <c r="I5" s="11" t="n"/>
-      <c r="J5" s="12" t="n"/>
-      <c r="K5" s="8" t="inlineStr"/>
-      <c r="L5" s="9" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M5" s="13" t="inlineStr">
-        <is>
-          <t>MA163
-LEC
-Room: 101
-Dr. Anand</t>
-        </is>
-      </c>
-      <c r="N5" s="12" t="n"/>
-      <c r="O5" s="8" t="inlineStr"/>
-      <c r="P5" s="8" t="inlineStr"/>
-      <c r="Q5" s="8" t="inlineStr"/>
-      <c r="R5" s="8" t="inlineStr"/>
-      <c r="S5" s="8" t="inlineStr"/>
-      <c r="T5" s="8" t="inlineStr"/>
-      <c r="U5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C6" s="14" t="inlineStr">
-        <is>
-          <t>CS162
-LEC
-Room: 101
-Dr. Guha</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="n"/>
-      <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="8" t="inlineStr"/>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>B1
-LEC</t>
-        </is>
-      </c>
-      <c r="H6" s="11" t="n"/>
-      <c r="I6" s="11" t="n"/>
-      <c r="J6" s="12" t="n"/>
-      <c r="K6" s="8" t="inlineStr"/>
-      <c r="L6" s="9" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M6" s="8" t="inlineStr"/>
-      <c r="N6" s="8" t="inlineStr"/>
-      <c r="O6" s="8" t="inlineStr"/>
-      <c r="P6" s="8" t="inlineStr"/>
-      <c r="Q6" s="8" t="inlineStr"/>
-      <c r="R6" s="8" t="inlineStr"/>
-      <c r="S6" s="8" t="inlineStr"/>
-      <c r="T6" s="8" t="inlineStr"/>
-      <c r="U6" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>Course Details</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>Course Code</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>Color</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>Name of the Course</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>Course Co-ordinator</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>LTPSC</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>Room Number</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>B1-CS154</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr"/>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>Intro Data Analytics</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr"/>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>Data Analytics</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>Dr. Abdul</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>3-1-0-0-2</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t>103</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>B1-EC156</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr"/>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>Intro Sensors</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr"/>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>Sensor Tech</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>Dr. Eswaran</t>
         </is>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>3-1-0-0-2</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>B1-ASD152</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr"/>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>Visual Design</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>Dr. Sandesh</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>3-1-0-0-2</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t>102</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>B1-ASD152</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr"/>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>Visual Design</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>Dr. Sandesh</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="21" t="inlineStr">
+        <is>
+          <t>B2-DS151</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr"/>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>Linux</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>Dr. Layek</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>3-1-0-0-2</t>
         </is>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="21" t="inlineStr">
+        <is>
+          <t>B2-CS151</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr"/>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>Cybersecurity</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>Dr. Rajendra</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>3-1-0-0-2</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="17" t="inlineStr">
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="21" t="inlineStr">
+        <is>
+          <t>B4-HS159</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr"/>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>Quantum Physics</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>Dr. Physics</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>3-1-0-0-2</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="21" t="inlineStr">
         <is>
           <t>MA163</t>
         </is>
       </c>
-      <c r="B15" s="19" t="inlineStr"/>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="B18" s="25" t="inlineStr"/>
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>Linear Algebra</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>Dr. Anand</t>
         </is>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="E18" s="21" t="inlineStr">
         <is>
           <t>3-1-0-0-2</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="17" t="inlineStr">
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="21" t="inlineStr">
         <is>
           <t>CS162</t>
         </is>
       </c>
-      <c r="B16" s="20" t="inlineStr"/>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="B19" s="26" t="inlineStr"/>
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>Optimization</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>Dr. Guha</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>3-1-0-0-2</t>
         </is>
       </c>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="21" t="inlineStr">
+        <is>
+          <t>CS163</t>
+        </is>
+      </c>
+      <c r="B20" s="27" t="inlineStr"/>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>Data Structures</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>Dr. Vivekraj</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>3-0-2-0-4</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="21" t="inlineStr">
+        <is>
+          <t>CS208</t>
+        </is>
+      </c>
+      <c r="B21" s="28" t="inlineStr"/>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>Computer Architecture</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>Dr. Prabhu</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>3-0-2-0-2</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="C6:D6"/>
+  <mergeCells count="15">
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="Q4:S4"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="P6:R6"/>
     <mergeCell ref="M5:N5"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="Q3:S3"/>
+    <mergeCell ref="D5:G5"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="C4:D4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1838,7 +2298,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1893,19 +2353,19 @@
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Dr. Abdul</t>
+          <t>Dr. Vivekraj</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1915,7 +2375,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CS154</t>
+          <t>CS163</t>
         </is>
       </c>
     </row>
@@ -1929,19 +2389,19 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dr. Eswaran</t>
+          <t>Dr. Abdul</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1951,7 +2411,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>EC156</t>
+          <t>CS154</t>
         </is>
       </c>
     </row>
@@ -1965,14 +2425,14 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dr. Sandesh</t>
+          <t>Dr. Eswaran</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1987,7 +2447,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ASD152</t>
+          <t>EC156</t>
         </is>
       </c>
     </row>
@@ -1998,32 +2458,32 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
         <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dr. Abdul</t>
+          <t>Dr. Sandesh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CS154</t>
+          <t>ASD152</t>
         </is>
       </c>
     </row>
@@ -2034,17 +2494,17 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dr. Eswaran</t>
+          <t>Dr. Anand</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -2059,7 +2519,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>EC156</t>
+          <t>MA163</t>
         </is>
       </c>
     </row>
@@ -2073,29 +2533,29 @@
         <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dr. Sandesh</t>
+          <t>Dr. Vivekraj</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>L101+L102</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LAB</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ASD152</t>
+          <t>CS163</t>
         </is>
       </c>
     </row>
@@ -2109,19 +2569,19 @@
         <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dr. Anand</t>
+          <t>Dr. Vivekraj</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2131,7 +2591,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>MA163</t>
+          <t>CS163</t>
         </is>
       </c>
     </row>
@@ -2142,22 +2602,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dr. Guha</t>
+          <t>Dr. Physics</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2167,7 +2627,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>CS162</t>
+          <t>HS159</t>
         </is>
       </c>
     </row>
@@ -2178,17 +2638,17 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dr. Guha</t>
+          <t>Dr. Prabhu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2203,7 +2663,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>CS162</t>
+          <t>CS208</t>
         </is>
       </c>
     </row>
@@ -2214,22 +2674,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dr. Anand</t>
+          <t>Dr. Layek</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2239,7 +2699,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>MA163</t>
+          <t>DS151</t>
         </is>
       </c>
     </row>
@@ -2250,17 +2710,17 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" t="n">
         <v>6</v>
       </c>
-      <c r="C12" t="n">
-        <v>3</v>
-      </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dr. Guha</t>
+          <t>Dr. Rajendra</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2275,7 +2735,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>CS162</t>
+          <t>CS151</t>
         </is>
       </c>
     </row>
@@ -2286,13 +2746,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C13" t="n">
         <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -2306,7 +2766,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2322,13 +2782,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
         <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -2342,7 +2802,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2358,13 +2818,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
         <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -2378,7 +2838,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2390,26 +2850,26 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CSE_2_B</t>
+          <t>CSE_2_A</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dr. Abdul</t>
+          <t>Dr. Guha</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2419,18 +2879,18 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>CS154</t>
+          <t>CS162</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CSE_2_B</t>
+          <t>CSE_2_A</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C17" t="n">
         <v>17</v>
@@ -2440,12 +2900,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dr. Eswaran</t>
+          <t>Dr. Anand</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2455,33 +2915,33 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>EC156</t>
+          <t>MA163</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CSE_2_B</t>
+          <t>CSE_2_A</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dr. Sandesh</t>
+          <t>Dr. Layek</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2491,64 +2951,64 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>ASD152</t>
+          <t>DS151</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CSE_2_B</t>
+          <t>CSE_2_A</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dr. Abdul</t>
+          <t>Dr. Rajendra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>CS154</t>
+          <t>CS151</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CSE_2_B</t>
+          <t>CSE_2_A</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D20" t="n">
         <v>14</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dr. Eswaran</t>
+          <t>Dr. Guha</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2558,105 +3018,105 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>EC156</t>
+          <t>CS162</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CSE_2_B</t>
+          <t>CSE_2_A</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C21" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D21" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dr. Sandesh</t>
+          <t>Dr. Physics</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>ASD152</t>
+          <t>HS159</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CSE_2_B</t>
+          <t>CSE_2_A</t>
         </is>
       </c>
       <c r="B22" t="n">
+        <v>6</v>
+      </c>
+      <c r="C22" t="n">
         <v>3</v>
       </c>
-      <c r="C22" t="n">
-        <v>17</v>
-      </c>
       <c r="D22" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dr. Anand</t>
+          <t>Dr. Layek</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>MA163</t>
+          <t>DS151</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CSE_2_B</t>
+          <t>CSE_2_A</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C23" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dr. Guha</t>
+          <t>Dr. Rajendra</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2671,33 +3131,33 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>CS162</t>
+          <t>CS151</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CSE_2_B</t>
+          <t>CSE_2_A</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dr. Guha</t>
+          <t>Dr. Abdul</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2707,28 +3167,28 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>CS162</t>
+          <t>CS154</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CSE_2_B</t>
+          <t>CSE_2_A</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C25" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dr. Anand</t>
+          <t>Dr. Eswaran</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2743,33 +3203,33 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>MA163</t>
+          <t>EC156</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CSE_2_B</t>
+          <t>CSE_2_A</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dr. Guha</t>
+          <t>Dr. Sandesh</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2779,28 +3239,28 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>CS162</t>
+          <t>ASD152</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CSE_2_B</t>
+          <t>CSE_2_A</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dr. Abdul</t>
+          <t>Dr. Physics</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2815,33 +3275,33 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>CS154</t>
+          <t>HS159</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CSE_2_B</t>
+          <t>CSE_2_A</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>6</v>
       </c>
       <c r="C28" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dr. Eswaran</t>
+          <t>Dr. Anand</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2851,7 +3311,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>EC156</t>
+          <t>MA163</t>
         </is>
       </c>
     </row>
@@ -2862,32 +3322,968 @@
         </is>
       </c>
       <c r="B29" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" t="n">
+        <v>5</v>
+      </c>
+      <c r="D29" t="n">
+        <v>8</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Dr. Vivekraj</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>LEC</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>CS163</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CSE_2_B</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" t="n">
+        <v>14</v>
+      </c>
+      <c r="D30" t="n">
+        <v>16</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Dr. Abdul</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>LEC</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>CS154</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CSE_2_B</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" t="n">
+        <v>14</v>
+      </c>
+      <c r="D31" t="n">
+        <v>16</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Dr. Eswaran</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>LEC</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>EC156</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>CSE_2_B</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" t="n">
+        <v>14</v>
+      </c>
+      <c r="D32" t="n">
+        <v>16</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Dr. Sandesh</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>LEC</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>ASD152</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>CSE_2_B</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" t="n">
+        <v>18</v>
+      </c>
+      <c r="D33" t="n">
+        <v>19</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Dr. Anand</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>MA163</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>CSE_2_B</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D34" t="n">
+        <v>8</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Dr. Vivekraj</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>L101+L102</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>LAB</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>CS163</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>CSE_2_B</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>3</v>
+      </c>
+      <c r="C35" t="n">
+        <v>14</v>
+      </c>
+      <c r="D35" t="n">
+        <v>16</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Dr. Vivekraj</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>LEC</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>CS163</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>CSE_2_B</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>3</v>
+      </c>
+      <c r="C36" t="n">
+        <v>20</v>
+      </c>
+      <c r="D36" t="n">
+        <v>20</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Dr. Physics</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>HS159</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>CSE_2_B</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>4</v>
+      </c>
+      <c r="C37" t="n">
+        <v>3</v>
+      </c>
+      <c r="D37" t="n">
+        <v>4</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Dr. Prabhu</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>LEC</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>CS208</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>CSE_2_B</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>4</v>
+      </c>
+      <c r="C38" t="n">
         <v>6</v>
       </c>
-      <c r="C29" t="n">
+      <c r="D38" t="n">
+        <v>6</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Dr. Layek</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>LEC</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>DS151</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>CSE_2_B</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>4</v>
+      </c>
+      <c r="C39" t="n">
+        <v>6</v>
+      </c>
+      <c r="D39" t="n">
+        <v>6</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Dr. Rajendra</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>LEC</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>CS151</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>CSE_2_B</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>4</v>
+      </c>
+      <c r="C40" t="n">
         <v>7</v>
       </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
+      <c r="D40" t="n">
+        <v>9</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Dr. Abdul</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>CS154</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>CSE_2_B</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>4</v>
+      </c>
+      <c r="C41" t="n">
+        <v>7</v>
+      </c>
+      <c r="D41" t="n">
+        <v>9</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Dr. Eswaran</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>EC156</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>CSE_2_B</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>4</v>
+      </c>
+      <c r="C42" t="n">
+        <v>7</v>
+      </c>
+      <c r="D42" t="n">
+        <v>9</v>
+      </c>
+      <c r="E42" t="inlineStr">
         <is>
           <t>Dr. Sandesh</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>ASD152</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>CSE_2_B</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>4</v>
+      </c>
+      <c r="C43" t="n">
+        <v>13</v>
+      </c>
+      <c r="D43" t="n">
+        <v>14</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Dr. Guha</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
         <is>
           <t>LEC</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>CS162</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>CSE_2_B</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>4</v>
+      </c>
+      <c r="C44" t="n">
+        <v>17</v>
+      </c>
+      <c r="D44" t="n">
+        <v>19</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Dr. Anand</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>LEC</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>MA163</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>CSE_2_B</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>5</v>
+      </c>
+      <c r="C45" t="n">
+        <v>4</v>
+      </c>
+      <c r="D45" t="n">
+        <v>7</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Dr. Layek</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>LEC</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>DS151</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>CSE_2_B</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>5</v>
+      </c>
+      <c r="C46" t="n">
+        <v>4</v>
+      </c>
+      <c r="D46" t="n">
+        <v>7</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Dr. Rajendra</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>LEC</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>CS151</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>CSE_2_B</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>5</v>
+      </c>
+      <c r="C47" t="n">
+        <v>13</v>
+      </c>
+      <c r="D47" t="n">
+        <v>14</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Dr. Guha</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>LEC</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>CS162</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>CSE_2_B</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>5</v>
+      </c>
+      <c r="C48" t="n">
+        <v>17</v>
+      </c>
+      <c r="D48" t="n">
+        <v>19</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Dr. Physics</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>LEC</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>HS159</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>CSE_2_B</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>6</v>
+      </c>
+      <c r="C49" t="n">
+        <v>3</v>
+      </c>
+      <c r="D49" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Dr. Layek</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>DS151</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>CSE_2_B</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>6</v>
+      </c>
+      <c r="C50" t="n">
+        <v>3</v>
+      </c>
+      <c r="D50" t="n">
+        <v>3</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Dr. Rajendra</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>CS151</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>CSE_2_B</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>6</v>
+      </c>
+      <c r="C51" t="n">
+        <v>6</v>
+      </c>
+      <c r="D51" t="n">
+        <v>9</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Dr. Abdul</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>LEC</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>CS154</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>CSE_2_B</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>6</v>
+      </c>
+      <c r="C52" t="n">
+        <v>6</v>
+      </c>
+      <c r="D52" t="n">
+        <v>9</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Dr. Eswaran</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>LEC</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>EC156</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>CSE_2_B</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>6</v>
+      </c>
+      <c r="C53" t="n">
+        <v>6</v>
+      </c>
+      <c r="D53" t="n">
+        <v>9</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Dr. Sandesh</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>LEC</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
         <is>
           <t>ASD152</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>CSE_2_B</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>6</v>
+      </c>
+      <c r="C54" t="n">
+        <v>13</v>
+      </c>
+      <c r="D54" t="n">
+        <v>14</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Dr. Physics</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>LEC</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>HS159</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>CSE_2_B</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>6</v>
+      </c>
+      <c r="C55" t="n">
+        <v>16</v>
+      </c>
+      <c r="D55" t="n">
+        <v>18</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Dr. Anand</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>LEC</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>MA163</t>
         </is>
       </c>
     </row>

--- a/tests/TC-11/results/timetable_all_departments_even.xlsx
+++ b/tests/TC-11/results/timetable_all_departments_even.xlsx
@@ -78,18 +78,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E1BEE7"/>
-        <bgColor rgb="00E1BEE7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E0E0E0"/>
-        <bgColor rgb="00E0E0E0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFDAB3"/>
         <bgColor rgb="00FFDAB3"/>
       </patternFill>
@@ -102,8 +90,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CDEFEA"/>
-        <bgColor rgb="00CDEFEA"/>
+        <fgColor rgb="00E0E0E0"/>
+        <bgColor rgb="00E0E0E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3BF"/>
+        <bgColor rgb="00FFF3BF"/>
       </patternFill>
     </fill>
     <fill>
@@ -114,8 +108,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3BF"/>
-        <bgColor rgb="00FFF3BF"/>
+        <fgColor rgb="00E1BEE7"/>
+        <bgColor rgb="00E1BEE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CDEFEA"/>
+        <bgColor rgb="00CDEFEA"/>
       </patternFill>
     </fill>
     <fill>
@@ -167,14 +167,14 @@
     </border>
     <border>
       <left/>
-      <right/>
+      <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin"/>
+      <right/>
       <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
@@ -206,17 +206,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -240,25 +240,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
@@ -861,9 +861,75 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr"/>
-      <c r="D2" s="8" t="inlineStr"/>
-      <c r="E2" s="9" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>B1
+LEC</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="n"/>
+      <c r="E2" s="10" t="inlineStr"/>
+      <c r="F2" s="11" t="inlineStr">
+        <is>
+          <t>MA163
+LEC
+Room: 101
+Dr. Anand</t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="n"/>
+      <c r="H2" s="12" t="n"/>
+      <c r="I2" s="9" t="n"/>
+      <c r="J2" s="10" t="inlineStr"/>
+      <c r="K2" s="10" t="inlineStr"/>
+      <c r="L2" s="13" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M2" s="14" t="inlineStr">
+        <is>
+          <t>CS162
+LEC
+Room: 102
+Dr. Guha</t>
+        </is>
+      </c>
+      <c r="N2" s="9" t="n"/>
+      <c r="O2" s="10" t="inlineStr"/>
+      <c r="P2" s="15" t="inlineStr">
+        <is>
+          <t>B4
+LEC</t>
+        </is>
+      </c>
+      <c r="Q2" s="12" t="n"/>
+      <c r="R2" s="9" t="n"/>
+      <c r="S2" s="10" t="inlineStr"/>
+      <c r="T2" s="16" t="inlineStr">
+        <is>
+          <t>B2
+TUT</t>
+        </is>
+      </c>
+      <c r="U2" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
         <is>
           <t>CS163
 LEC
@@ -871,56 +937,211 @@
 Dr. Vivekraj</t>
         </is>
       </c>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="10" t="n"/>
-      <c r="H2" s="11" t="n"/>
-      <c r="I2" s="8" t="inlineStr"/>
-      <c r="J2" s="8" t="inlineStr"/>
-      <c r="K2" s="8" t="inlineStr"/>
-      <c r="L2" s="12" t="inlineStr">
+      <c r="D3" s="9" t="n"/>
+      <c r="E3" s="10" t="inlineStr"/>
+      <c r="F3" s="10" t="inlineStr"/>
+      <c r="G3" s="10" t="inlineStr"/>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>B1
+TUT</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="n"/>
+      <c r="J3" s="9" t="n"/>
+      <c r="K3" s="10" t="inlineStr"/>
+      <c r="L3" s="13" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M2" s="8" t="inlineStr"/>
-      <c r="N2" s="13" t="inlineStr">
+      <c r="M3" s="16" t="inlineStr">
+        <is>
+          <t>B2
+LEC</t>
+        </is>
+      </c>
+      <c r="N3" s="9" t="n"/>
+      <c r="O3" s="10" t="inlineStr"/>
+      <c r="P3" s="10" t="inlineStr"/>
+      <c r="Q3" s="10" t="inlineStr"/>
+      <c r="R3" s="11" t="inlineStr">
+        <is>
+          <t>MA163
+TUT
+Room: 101
+Dr. Anand</t>
+        </is>
+      </c>
+      <c r="S3" s="9" t="n"/>
+      <c r="T3" s="10" t="inlineStr"/>
+      <c r="U3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr"/>
+      <c r="D4" s="10" t="inlineStr"/>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>B2
+LEC</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="n"/>
+      <c r="G4" s="12" t="n"/>
+      <c r="H4" s="9" t="n"/>
+      <c r="I4" s="10" t="inlineStr"/>
+      <c r="J4" s="15" t="inlineStr">
+        <is>
+          <t>B4
+TUT</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="n"/>
+      <c r="L4" s="13" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M4" s="11" t="inlineStr">
+        <is>
+          <t>MA163
+LEC
+Room: 101
+Dr. Anand</t>
+        </is>
+      </c>
+      <c r="N4" s="9" t="n"/>
+      <c r="O4" s="10" t="inlineStr"/>
+      <c r="P4" s="10" t="inlineStr"/>
+      <c r="Q4" s="8" t="inlineStr">
         <is>
           <t>B1
 LEC</t>
         </is>
       </c>
-      <c r="O2" s="10" t="n"/>
-      <c r="P2" s="11" t="n"/>
-      <c r="Q2" s="8" t="inlineStr"/>
-      <c r="R2" s="14" t="inlineStr">
-        <is>
-          <t>MA163
+      <c r="R4" s="12" t="n"/>
+      <c r="S4" s="9" t="n"/>
+      <c r="T4" s="10" t="inlineStr"/>
+      <c r="U4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr"/>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>B4
+LEC</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="n"/>
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="9" t="n"/>
+      <c r="H5" s="10" t="inlineStr"/>
+      <c r="I5" s="10" t="inlineStr"/>
+      <c r="J5" s="10" t="inlineStr"/>
+      <c r="K5" s="10" t="inlineStr"/>
+      <c r="L5" s="13" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M5" s="10" t="inlineStr"/>
+      <c r="N5" s="17" t="inlineStr">
+        <is>
+          <t>CS163
+LEC
+Room: 102
+Dr. Vivekraj</t>
+        </is>
+      </c>
+      <c r="O5" s="12" t="n"/>
+      <c r="P5" s="9" t="n"/>
+      <c r="Q5" s="10" t="inlineStr"/>
+      <c r="R5" s="14" t="inlineStr">
+        <is>
+          <t>CS162
 TUT
 Room: 102
-Dr. Anand</t>
-        </is>
-      </c>
-      <c r="S2" s="11" t="n"/>
-      <c r="T2" s="8" t="inlineStr"/>
-      <c r="U2" s="7" t="inlineStr">
+Dr. Guha</t>
+        </is>
+      </c>
+      <c r="S5" s="9" t="n"/>
+      <c r="T5" s="10" t="inlineStr"/>
+      <c r="U5" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="40" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr"/>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr"/>
+      <c r="D6" s="10" t="inlineStr"/>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>CS162
+LEC
+Room: 102
+Dr. Guha</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="12" t="n"/>
+      <c r="H6" s="9" t="n"/>
+      <c r="I6" s="10" t="inlineStr"/>
+      <c r="J6" s="10" t="inlineStr"/>
+      <c r="K6" s="10" t="inlineStr"/>
+      <c r="L6" s="13" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M6" s="18" t="inlineStr">
+        <is>
+          <t>CS208
+LEC
+Room: 101
+Dr. Prabhu</t>
+        </is>
+      </c>
+      <c r="N6" s="9" t="n"/>
+      <c r="O6" s="17" t="inlineStr">
         <is>
           <t>CS163
 LAB
@@ -928,232 +1149,11 @@
 Dr. Vivekraj</t>
         </is>
       </c>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="10" t="n"/>
-      <c r="G3" s="10" t="n"/>
-      <c r="H3" s="11" t="n"/>
-      <c r="I3" s="8" t="inlineStr"/>
-      <c r="J3" s="8" t="inlineStr"/>
-      <c r="K3" s="8" t="inlineStr"/>
-      <c r="L3" s="12" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M3" s="8" t="inlineStr"/>
-      <c r="N3" s="9" t="inlineStr">
-        <is>
-          <t>CS163
-LEC
-Room: 102
-Dr. Vivekraj</t>
-        </is>
-      </c>
-      <c r="O3" s="10" t="n"/>
-      <c r="P3" s="11" t="n"/>
-      <c r="Q3" s="8" t="inlineStr"/>
-      <c r="R3" s="8" t="inlineStr"/>
-      <c r="S3" s="8" t="inlineStr"/>
-      <c r="T3" s="15" t="inlineStr">
-        <is>
-          <t>B4
-TUT</t>
-        </is>
-      </c>
-      <c r="U3" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="40" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C4" s="16" t="inlineStr">
-        <is>
-          <t>CS208
-LEC
-Room: 101
-Dr. Prabhu</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="8" t="inlineStr"/>
-      <c r="F4" s="17" t="inlineStr">
-        <is>
-          <t>B2
-LEC</t>
-        </is>
-      </c>
-      <c r="G4" s="13" t="inlineStr">
-        <is>
-          <t>B1
-TUT</t>
-        </is>
-      </c>
-      <c r="H4" s="10" t="n"/>
-      <c r="I4" s="11" t="n"/>
-      <c r="J4" s="8" t="inlineStr"/>
-      <c r="K4" s="8" t="inlineStr"/>
-      <c r="L4" s="12" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M4" s="18" t="inlineStr">
-        <is>
-          <t>CS162
-LEC
-Room: 102
-Dr. Guha</t>
-        </is>
-      </c>
-      <c r="N4" s="11" t="n"/>
-      <c r="O4" s="8" t="inlineStr"/>
-      <c r="P4" s="8" t="inlineStr"/>
-      <c r="Q4" s="14" t="inlineStr">
-        <is>
-          <t>MA163
-LEC
-Room: 101
-Dr. Anand</t>
-        </is>
-      </c>
-      <c r="R4" s="10" t="n"/>
-      <c r="S4" s="11" t="n"/>
-      <c r="T4" s="8" t="inlineStr"/>
-      <c r="U4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr"/>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>B2
-LEC</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="n"/>
-      <c r="F5" s="10" t="n"/>
-      <c r="G5" s="11" t="n"/>
-      <c r="H5" s="8" t="inlineStr"/>
-      <c r="I5" s="8" t="inlineStr"/>
-      <c r="J5" s="8" t="inlineStr"/>
-      <c r="K5" s="8" t="inlineStr"/>
-      <c r="L5" s="12" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M5" s="18" t="inlineStr">
-        <is>
-          <t>CS162
-LEC
-Room: 102
-Dr. Guha</t>
-        </is>
-      </c>
-      <c r="N5" s="11" t="n"/>
-      <c r="O5" s="8" t="inlineStr"/>
-      <c r="P5" s="8" t="inlineStr"/>
-      <c r="Q5" s="15" t="inlineStr">
-        <is>
-          <t>B4
-LEC</t>
-        </is>
-      </c>
-      <c r="R5" s="10" t="n"/>
-      <c r="S5" s="11" t="n"/>
-      <c r="T5" s="8" t="inlineStr"/>
-      <c r="U5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>B2
-TUT</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr"/>
-      <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="13" t="inlineStr">
-        <is>
-          <t>B1
-LEC</t>
-        </is>
-      </c>
-      <c r="G6" s="10" t="n"/>
-      <c r="H6" s="10" t="n"/>
-      <c r="I6" s="11" t="n"/>
-      <c r="J6" s="8" t="inlineStr"/>
-      <c r="K6" s="8" t="inlineStr"/>
-      <c r="L6" s="12" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M6" s="15" t="inlineStr">
-        <is>
-          <t>B4
-LEC</t>
-        </is>
-      </c>
-      <c r="N6" s="11" t="n"/>
-      <c r="O6" s="8" t="inlineStr"/>
-      <c r="P6" s="14" t="inlineStr">
-        <is>
-          <t>MA163
-LEC
-Room: 101
-Dr. Anand</t>
-        </is>
-      </c>
-      <c r="Q6" s="10" t="n"/>
-      <c r="R6" s="11" t="n"/>
-      <c r="S6" s="8" t="inlineStr"/>
-      <c r="T6" s="18" t="inlineStr">
-        <is>
-          <t>CS162
-TUT
-Room: 101
-Dr. Guha</t>
-        </is>
-      </c>
+      <c r="P6" s="12" t="n"/>
+      <c r="Q6" s="12" t="n"/>
+      <c r="R6" s="12" t="n"/>
+      <c r="S6" s="9" t="n"/>
+      <c r="T6" s="10" t="inlineStr"/>
       <c r="U6" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="F13" s="21" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
     </row>
@@ -1480,22 +1480,25 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="Q5:S5"/>
-    <mergeCell ref="N2:P2"/>
+  <mergeCells count="18">
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="C2:D2"/>
     <mergeCell ref="M6:N6"/>
-    <mergeCell ref="F6:I6"/>
-    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="P2:R2"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="E4:H4"/>
     <mergeCell ref="Q4:S4"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="O6:S6"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="H3:J3"/>
     <mergeCell ref="D5:G5"/>
+    <mergeCell ref="C3:D3"/>
     <mergeCell ref="M4:N4"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="R5:S5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1652,9 +1655,75 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr"/>
-      <c r="D2" s="8" t="inlineStr"/>
-      <c r="E2" s="9" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>B1
+LEC</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="n"/>
+      <c r="E2" s="10" t="inlineStr"/>
+      <c r="F2" s="11" t="inlineStr">
+        <is>
+          <t>MA163
+LEC
+Room: 101
+Dr. Anand</t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="n"/>
+      <c r="H2" s="12" t="n"/>
+      <c r="I2" s="9" t="n"/>
+      <c r="J2" s="10" t="inlineStr"/>
+      <c r="K2" s="10" t="inlineStr"/>
+      <c r="L2" s="13" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M2" s="14" t="inlineStr">
+        <is>
+          <t>CS162
+LEC
+Room: 102
+Dr. Guha</t>
+        </is>
+      </c>
+      <c r="N2" s="9" t="n"/>
+      <c r="O2" s="10" t="inlineStr"/>
+      <c r="P2" s="15" t="inlineStr">
+        <is>
+          <t>B4
+LEC</t>
+        </is>
+      </c>
+      <c r="Q2" s="12" t="n"/>
+      <c r="R2" s="9" t="n"/>
+      <c r="S2" s="10" t="inlineStr"/>
+      <c r="T2" s="16" t="inlineStr">
+        <is>
+          <t>B2
+TUT</t>
+        </is>
+      </c>
+      <c r="U2" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
         <is>
           <t>CS163
 LEC
@@ -1662,56 +1731,211 @@
 Dr. Vivekraj</t>
         </is>
       </c>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="10" t="n"/>
-      <c r="H2" s="11" t="n"/>
-      <c r="I2" s="8" t="inlineStr"/>
-      <c r="J2" s="8" t="inlineStr"/>
-      <c r="K2" s="8" t="inlineStr"/>
-      <c r="L2" s="12" t="inlineStr">
+      <c r="D3" s="9" t="n"/>
+      <c r="E3" s="10" t="inlineStr"/>
+      <c r="F3" s="10" t="inlineStr"/>
+      <c r="G3" s="10" t="inlineStr"/>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>B1
+TUT</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="n"/>
+      <c r="J3" s="9" t="n"/>
+      <c r="K3" s="10" t="inlineStr"/>
+      <c r="L3" s="13" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M2" s="8" t="inlineStr"/>
-      <c r="N2" s="13" t="inlineStr">
+      <c r="M3" s="16" t="inlineStr">
+        <is>
+          <t>B2
+LEC</t>
+        </is>
+      </c>
+      <c r="N3" s="9" t="n"/>
+      <c r="O3" s="10" t="inlineStr"/>
+      <c r="P3" s="10" t="inlineStr"/>
+      <c r="Q3" s="10" t="inlineStr"/>
+      <c r="R3" s="11" t="inlineStr">
+        <is>
+          <t>MA163
+TUT
+Room: 101
+Dr. Anand</t>
+        </is>
+      </c>
+      <c r="S3" s="9" t="n"/>
+      <c r="T3" s="10" t="inlineStr"/>
+      <c r="U3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr"/>
+      <c r="D4" s="10" t="inlineStr"/>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>B2
+LEC</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="n"/>
+      <c r="G4" s="12" t="n"/>
+      <c r="H4" s="9" t="n"/>
+      <c r="I4" s="10" t="inlineStr"/>
+      <c r="J4" s="15" t="inlineStr">
+        <is>
+          <t>B4
+TUT</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="n"/>
+      <c r="L4" s="13" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M4" s="11" t="inlineStr">
+        <is>
+          <t>MA163
+LEC
+Room: 101
+Dr. Anand</t>
+        </is>
+      </c>
+      <c r="N4" s="9" t="n"/>
+      <c r="O4" s="10" t="inlineStr"/>
+      <c r="P4" s="10" t="inlineStr"/>
+      <c r="Q4" s="8" t="inlineStr">
         <is>
           <t>B1
 LEC</t>
         </is>
       </c>
-      <c r="O2" s="10" t="n"/>
-      <c r="P2" s="11" t="n"/>
-      <c r="Q2" s="8" t="inlineStr"/>
-      <c r="R2" s="14" t="inlineStr">
-        <is>
-          <t>MA163
+      <c r="R4" s="12" t="n"/>
+      <c r="S4" s="9" t="n"/>
+      <c r="T4" s="10" t="inlineStr"/>
+      <c r="U4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr"/>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>B4
+LEC</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="n"/>
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="9" t="n"/>
+      <c r="H5" s="10" t="inlineStr"/>
+      <c r="I5" s="10" t="inlineStr"/>
+      <c r="J5" s="10" t="inlineStr"/>
+      <c r="K5" s="10" t="inlineStr"/>
+      <c r="L5" s="13" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M5" s="10" t="inlineStr"/>
+      <c r="N5" s="17" t="inlineStr">
+        <is>
+          <t>CS163
+LEC
+Room: 102
+Dr. Vivekraj</t>
+        </is>
+      </c>
+      <c r="O5" s="12" t="n"/>
+      <c r="P5" s="9" t="n"/>
+      <c r="Q5" s="10" t="inlineStr"/>
+      <c r="R5" s="14" t="inlineStr">
+        <is>
+          <t>CS162
 TUT
 Room: 102
-Dr. Anand</t>
-        </is>
-      </c>
-      <c r="S2" s="11" t="n"/>
-      <c r="T2" s="8" t="inlineStr"/>
-      <c r="U2" s="7" t="inlineStr">
+Dr. Guha</t>
+        </is>
+      </c>
+      <c r="S5" s="9" t="n"/>
+      <c r="T5" s="10" t="inlineStr"/>
+      <c r="U5" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="40" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr"/>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr"/>
+      <c r="D6" s="10" t="inlineStr"/>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>CS162
+LEC
+Room: 102
+Dr. Guha</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="12" t="n"/>
+      <c r="H6" s="9" t="n"/>
+      <c r="I6" s="10" t="inlineStr"/>
+      <c r="J6" s="10" t="inlineStr"/>
+      <c r="K6" s="10" t="inlineStr"/>
+      <c r="L6" s="13" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M6" s="18" t="inlineStr">
+        <is>
+          <t>CS208
+LEC
+Room: 101
+Dr. Prabhu</t>
+        </is>
+      </c>
+      <c r="N6" s="9" t="n"/>
+      <c r="O6" s="17" t="inlineStr">
         <is>
           <t>CS163
 LAB
@@ -1719,232 +1943,11 @@
 Dr. Vivekraj</t>
         </is>
       </c>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="10" t="n"/>
-      <c r="G3" s="10" t="n"/>
-      <c r="H3" s="11" t="n"/>
-      <c r="I3" s="8" t="inlineStr"/>
-      <c r="J3" s="8" t="inlineStr"/>
-      <c r="K3" s="8" t="inlineStr"/>
-      <c r="L3" s="12" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M3" s="8" t="inlineStr"/>
-      <c r="N3" s="9" t="inlineStr">
-        <is>
-          <t>CS163
-LEC
-Room: 102
-Dr. Vivekraj</t>
-        </is>
-      </c>
-      <c r="O3" s="10" t="n"/>
-      <c r="P3" s="11" t="n"/>
-      <c r="Q3" s="8" t="inlineStr"/>
-      <c r="R3" s="8" t="inlineStr"/>
-      <c r="S3" s="8" t="inlineStr"/>
-      <c r="T3" s="15" t="inlineStr">
-        <is>
-          <t>B4
-TUT</t>
-        </is>
-      </c>
-      <c r="U3" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="40" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C4" s="16" t="inlineStr">
-        <is>
-          <t>CS208
-LEC
-Room: 101
-Dr. Prabhu</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="n"/>
-      <c r="E4" s="8" t="inlineStr"/>
-      <c r="F4" s="17" t="inlineStr">
-        <is>
-          <t>B2
-LEC</t>
-        </is>
-      </c>
-      <c r="G4" s="13" t="inlineStr">
-        <is>
-          <t>B1
-TUT</t>
-        </is>
-      </c>
-      <c r="H4" s="10" t="n"/>
-      <c r="I4" s="11" t="n"/>
-      <c r="J4" s="8" t="inlineStr"/>
-      <c r="K4" s="8" t="inlineStr"/>
-      <c r="L4" s="12" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M4" s="18" t="inlineStr">
-        <is>
-          <t>CS162
-LEC
-Room: 102
-Dr. Guha</t>
-        </is>
-      </c>
-      <c r="N4" s="11" t="n"/>
-      <c r="O4" s="8" t="inlineStr"/>
-      <c r="P4" s="8" t="inlineStr"/>
-      <c r="Q4" s="14" t="inlineStr">
-        <is>
-          <t>MA163
-LEC
-Room: 101
-Dr. Anand</t>
-        </is>
-      </c>
-      <c r="R4" s="10" t="n"/>
-      <c r="S4" s="11" t="n"/>
-      <c r="T4" s="8" t="inlineStr"/>
-      <c r="U4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr"/>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>B2
-LEC</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="n"/>
-      <c r="F5" s="10" t="n"/>
-      <c r="G5" s="11" t="n"/>
-      <c r="H5" s="8" t="inlineStr"/>
-      <c r="I5" s="8" t="inlineStr"/>
-      <c r="J5" s="8" t="inlineStr"/>
-      <c r="K5" s="8" t="inlineStr"/>
-      <c r="L5" s="12" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M5" s="18" t="inlineStr">
-        <is>
-          <t>CS162
-LEC
-Room: 102
-Dr. Guha</t>
-        </is>
-      </c>
-      <c r="N5" s="11" t="n"/>
-      <c r="O5" s="8" t="inlineStr"/>
-      <c r="P5" s="8" t="inlineStr"/>
-      <c r="Q5" s="15" t="inlineStr">
-        <is>
-          <t>B4
-LEC</t>
-        </is>
-      </c>
-      <c r="R5" s="10" t="n"/>
-      <c r="S5" s="11" t="n"/>
-      <c r="T5" s="8" t="inlineStr"/>
-      <c r="U5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>B2
-TUT</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr"/>
-      <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="13" t="inlineStr">
-        <is>
-          <t>B1
-LEC</t>
-        </is>
-      </c>
-      <c r="G6" s="10" t="n"/>
-      <c r="H6" s="10" t="n"/>
-      <c r="I6" s="11" t="n"/>
-      <c r="J6" s="8" t="inlineStr"/>
-      <c r="K6" s="8" t="inlineStr"/>
-      <c r="L6" s="12" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M6" s="15" t="inlineStr">
-        <is>
-          <t>B4
-LEC</t>
-        </is>
-      </c>
-      <c r="N6" s="11" t="n"/>
-      <c r="O6" s="8" t="inlineStr"/>
-      <c r="P6" s="14" t="inlineStr">
-        <is>
-          <t>MA163
-LEC
-Room: 101
-Dr. Anand</t>
-        </is>
-      </c>
-      <c r="Q6" s="10" t="n"/>
-      <c r="R6" s="11" t="n"/>
-      <c r="S6" s="8" t="inlineStr"/>
-      <c r="T6" s="18" t="inlineStr">
-        <is>
-          <t>CS162
-TUT
-Room: 101
-Dr. Guha</t>
-        </is>
-      </c>
+      <c r="P6" s="12" t="n"/>
+      <c r="Q6" s="12" t="n"/>
+      <c r="R6" s="12" t="n"/>
+      <c r="S6" s="9" t="n"/>
+      <c r="T6" s="10" t="inlineStr"/>
       <c r="U6" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -2042,7 +2045,7 @@
       </c>
       <c r="F13" s="21" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2073,7 @@
       </c>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2157,7 @@
       </c>
       <c r="F17" s="21" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
     </row>
@@ -2271,22 +2274,25 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="Q5:S5"/>
-    <mergeCell ref="N2:P2"/>
+  <mergeCells count="18">
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="C2:D2"/>
     <mergeCell ref="M6:N6"/>
-    <mergeCell ref="F6:I6"/>
-    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="P2:R2"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="E4:H4"/>
     <mergeCell ref="Q4:S4"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="O6:S6"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="H3:J3"/>
     <mergeCell ref="D5:G5"/>
+    <mergeCell ref="C3:D3"/>
     <mergeCell ref="M4:N4"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="R5:S5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2298,7 +2304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2353,19 +2359,19 @@
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Dr. Vivekraj</t>
+          <t>Dr. Abdul</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -2375,7 +2381,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CS163</t>
+          <t>CS154</t>
         </is>
       </c>
     </row>
@@ -2389,19 +2395,19 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dr. Abdul</t>
+          <t>Dr. Eswaran</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -2411,7 +2417,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CS154</t>
+          <t>EC156</t>
         </is>
       </c>
     </row>
@@ -2425,14 +2431,14 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dr. Eswaran</t>
+          <t>Dr. Sandesh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -2447,7 +2453,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>EC156</t>
+          <t>ASD152</t>
         </is>
       </c>
     </row>
@@ -2461,19 +2467,19 @@
         <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dr. Sandesh</t>
+          <t>Dr. Anand</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2483,7 +2489,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ASD152</t>
+          <t>MA163</t>
         </is>
       </c>
     </row>
@@ -2497,14 +2503,14 @@
         <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dr. Anand</t>
+          <t>Dr. Guha</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -2514,12 +2520,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>MA163</t>
+          <t>CS162</t>
         </is>
       </c>
     </row>
@@ -2530,32 +2536,32 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dr. Vivekraj</t>
+          <t>Dr. Physics</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>L101+L102</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>LAB</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>CS163</t>
+          <t>HS159</t>
         </is>
       </c>
     </row>
@@ -2566,32 +2572,32 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dr. Vivekraj</t>
+          <t>Dr. Layek</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>CS163</t>
+          <t>DS151</t>
         </is>
       </c>
     </row>
@@ -2602,7 +2608,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
         <v>20</v>
@@ -2612,12 +2618,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dr. Physics</t>
+          <t>Dr. Rajendra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2627,7 +2633,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>HS159</t>
+          <t>CS151</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2644,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
         <v>3</v>
@@ -2648,12 +2654,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dr. Prabhu</t>
+          <t>Dr. Vivekraj</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2663,7 +2669,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>CS208</t>
+          <t>CS163</t>
         </is>
       </c>
     </row>
@@ -2674,17 +2680,17 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dr. Layek</t>
+          <t>Dr. Abdul</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2694,12 +2700,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>DS151</t>
+          <t>CS154</t>
         </is>
       </c>
     </row>
@@ -2710,17 +2716,17 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dr. Rajendra</t>
+          <t>Dr. Eswaran</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2730,12 +2736,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>CS151</t>
+          <t>EC156</t>
         </is>
       </c>
     </row>
@@ -2746,22 +2752,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dr. Abdul</t>
+          <t>Dr. Sandesh</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2771,7 +2777,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>CS154</t>
+          <t>ASD152</t>
         </is>
       </c>
     </row>
@@ -2782,32 +2788,32 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dr. Eswaran</t>
+          <t>Dr. Layek</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>EC156</t>
+          <t>DS151</t>
         </is>
       </c>
     </row>
@@ -2818,17 +2824,17 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D15" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dr. Sandesh</t>
+          <t>Dr. Rajendra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2838,12 +2844,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>ASD152</t>
+          <t>CS151</t>
         </is>
       </c>
     </row>
@@ -2854,32 +2860,32 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D16" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dr. Guha</t>
+          <t>Dr. Anand</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>CS162</t>
+          <t>MA163</t>
         </is>
       </c>
     </row>
@@ -2893,19 +2899,19 @@
         <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dr. Anand</t>
+          <t>Dr. Layek</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2915,7 +2921,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>MA163</t>
+          <t>DS151</t>
         </is>
       </c>
     </row>
@@ -2926,22 +2932,22 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>4</v>
+      </c>
+      <c r="C18" t="n">
         <v>5</v>
       </c>
-      <c r="C18" t="n">
-        <v>4</v>
-      </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dr. Layek</t>
+          <t>Dr. Rajendra</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2951,7 +2957,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>DS151</t>
+          <t>CS151</t>
         </is>
       </c>
     </row>
@@ -2962,32 +2968,32 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dr. Rajendra</t>
+          <t>Dr. Physics</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>CS151</t>
+          <t>HS159</t>
         </is>
       </c>
     </row>
@@ -2998,7 +3004,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C20" t="n">
         <v>13</v>
@@ -3008,12 +3014,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dr. Guha</t>
+          <t>Dr. Anand</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3023,7 +3029,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>CS162</t>
+          <t>MA163</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3040,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C21" t="n">
         <v>17</v>
@@ -3044,7 +3050,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dr. Physics</t>
+          <t>Dr. Abdul</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3059,7 +3065,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>HS159</t>
+          <t>CS154</t>
         </is>
       </c>
     </row>
@@ -3070,32 +3076,32 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dr. Layek</t>
+          <t>Dr. Eswaran</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>DS151</t>
+          <t>EC156</t>
         </is>
       </c>
     </row>
@@ -3106,17 +3112,17 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dr. Rajendra</t>
+          <t>Dr. Sandesh</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3126,12 +3132,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>CS151</t>
+          <t>ASD152</t>
         </is>
       </c>
     </row>
@@ -3142,17 +3148,17 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dr. Abdul</t>
+          <t>Dr. Physics</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3167,7 +3173,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>CS154</t>
+          <t>HS159</t>
         </is>
       </c>
     </row>
@@ -3178,22 +3184,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D25" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dr. Eswaran</t>
+          <t>Dr. Vivekraj</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3203,7 +3209,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>EC156</t>
+          <t>CS163</t>
         </is>
       </c>
     </row>
@@ -3214,17 +3220,17 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D26" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dr. Sandesh</t>
+          <t>Dr. Guha</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3234,12 +3240,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>ASD152</t>
+          <t>CS162</t>
         </is>
       </c>
     </row>
@@ -3253,19 +3259,19 @@
         <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dr. Physics</t>
+          <t>Dr. Guha</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3275,7 +3281,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>HS159</t>
+          <t>CS162</t>
         </is>
       </c>
     </row>
@@ -3289,14 +3295,14 @@
         <v>6</v>
       </c>
       <c r="C28" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D28" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dr. Anand</t>
+          <t>Dr. Prabhu</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3311,24 +3317,24 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>MA163</t>
+          <t>CS208</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CSE_2_B</t>
+          <t>CSE_2_A</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D29" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -3337,12 +3343,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>L101+L102</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>LAB</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3361,10 +3367,10 @@
         <v>2</v>
       </c>
       <c r="C30" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -3397,10 +3403,10 @@
         <v>2</v>
       </c>
       <c r="C31" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -3409,7 +3415,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3433,10 +3439,10 @@
         <v>2</v>
       </c>
       <c r="C32" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D32" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -3445,7 +3451,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3469,10 +3475,10 @@
         <v>2</v>
       </c>
       <c r="C33" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D33" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -3481,12 +3487,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3502,32 +3508,32 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D34" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dr. Vivekraj</t>
+          <t>Dr. Guha</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>L101+L102</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>LAB</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>CS163</t>
+          <t>CS162</t>
         </is>
       </c>
     </row>
@@ -3538,17 +3544,17 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C35" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D35" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dr. Vivekraj</t>
+          <t>Dr. Physics</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3563,7 +3569,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>CS163</t>
+          <t>HS159</t>
         </is>
       </c>
     </row>
@@ -3574,7 +3580,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C36" t="n">
         <v>20</v>
@@ -3584,12 +3590,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Dr. Physics</t>
+          <t>Dr. Layek</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3599,7 +3605,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>HS159</t>
+          <t>DS151</t>
         </is>
       </c>
     </row>
@@ -3610,17 +3616,17 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D37" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Dr. Prabhu</t>
+          <t>Dr. Rajendra</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3630,12 +3636,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>CS208</t>
+          <t>CS151</t>
         </is>
       </c>
     </row>
@@ -3646,17 +3652,17 @@
         </is>
       </c>
       <c r="B38" t="n">
+        <v>3</v>
+      </c>
+      <c r="C38" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" t="n">
         <v>4</v>
       </c>
-      <c r="C38" t="n">
-        <v>6</v>
-      </c>
-      <c r="D38" t="n">
-        <v>6</v>
-      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Dr. Layek</t>
+          <t>Dr. Vivekraj</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3671,7 +3677,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>DS151</t>
+          <t>CS163</t>
         </is>
       </c>
     </row>
@@ -3682,32 +3688,32 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C39" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D39" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Dr. Rajendra</t>
+          <t>Dr. Abdul</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>CS151</t>
+          <t>CS154</t>
         </is>
       </c>
     </row>
@@ -3718,22 +3724,22 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C40" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dr. Abdul</t>
+          <t>Dr. Eswaran</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3743,7 +3749,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>CS154</t>
+          <t>EC156</t>
         </is>
       </c>
     </row>
@@ -3754,17 +3760,17 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C41" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dr. Eswaran</t>
+          <t>Dr. Sandesh</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3779,7 +3785,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>EC156</t>
+          <t>ASD152</t>
         </is>
       </c>
     </row>
@@ -3790,32 +3796,32 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C42" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D42" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dr. Sandesh</t>
+          <t>Dr. Layek</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>ASD152</t>
+          <t>DS151</t>
         </is>
       </c>
     </row>
@@ -3826,7 +3832,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C43" t="n">
         <v>13</v>
@@ -3836,12 +3842,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dr. Guha</t>
+          <t>Dr. Rajendra</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3851,7 +3857,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>CS162</t>
+          <t>CS151</t>
         </is>
       </c>
     </row>
@@ -3862,10 +3868,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C44" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D44" t="n">
         <v>19</v>
@@ -3882,7 +3888,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3898,13 +3904,13 @@
         </is>
       </c>
       <c r="B45" t="n">
+        <v>4</v>
+      </c>
+      <c r="C45" t="n">
         <v>5</v>
       </c>
-      <c r="C45" t="n">
-        <v>4</v>
-      </c>
       <c r="D45" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -3934,13 +3940,13 @@
         </is>
       </c>
       <c r="B46" t="n">
+        <v>4</v>
+      </c>
+      <c r="C46" t="n">
         <v>5</v>
       </c>
-      <c r="C46" t="n">
-        <v>4</v>
-      </c>
       <c r="D46" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -3970,17 +3976,17 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C47" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D47" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dr. Guha</t>
+          <t>Dr. Physics</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3990,12 +3996,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>CS162</t>
+          <t>HS159</t>
         </is>
       </c>
     </row>
@@ -4006,17 +4012,17 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C48" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D48" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dr. Physics</t>
+          <t>Dr. Anand</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -4031,7 +4037,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>HS159</t>
+          <t>MA163</t>
         </is>
       </c>
     </row>
@@ -4042,32 +4048,32 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dr. Layek</t>
+          <t>Dr. Abdul</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>DS151</t>
+          <t>CS154</t>
         </is>
       </c>
     </row>
@@ -4078,32 +4084,32 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D50" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dr. Rajendra</t>
+          <t>Dr. Eswaran</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>CS151</t>
+          <t>EC156</t>
         </is>
       </c>
     </row>
@@ -4114,22 +4120,22 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C51" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D51" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dr. Abdul</t>
+          <t>Dr. Sandesh</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4139,7 +4145,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>CS154</t>
+          <t>ASD152</t>
         </is>
       </c>
     </row>
@@ -4150,22 +4156,22 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C52" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D52" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dr. Eswaran</t>
+          <t>Dr. Physics</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4175,7 +4181,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>EC156</t>
+          <t>HS159</t>
         </is>
       </c>
     </row>
@@ -4186,17 +4192,17 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C53" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D53" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dr. Sandesh</t>
+          <t>Dr. Vivekraj</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4211,7 +4217,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>ASD152</t>
+          <t>CS163</t>
         </is>
       </c>
     </row>
@@ -4222,32 +4228,32 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C54" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D54" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dr. Physics</t>
+          <t>Dr. Guha</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>HS159</t>
+          <t>CS162</t>
         </is>
       </c>
     </row>
@@ -4261,29 +4267,101 @@
         <v>6</v>
       </c>
       <c r="C55" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D55" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Dr. Anand</t>
+          <t>Dr. Guha</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>LEC</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>CS162</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>CSE_2_B</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>6</v>
+      </c>
+      <c r="C56" t="n">
+        <v>13</v>
+      </c>
+      <c r="D56" t="n">
+        <v>14</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Dr. Prabhu</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>LEC</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>MA163</t>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>CS208</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>CSE_2_B</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>6</v>
+      </c>
+      <c r="C57" t="n">
+        <v>15</v>
+      </c>
+      <c r="D57" t="n">
+        <v>19</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Dr. Vivekraj</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>L101+L102</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>LAB</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>CS163</t>
         </is>
       </c>
     </row>
